--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/maule.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/maule.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>3388.55</v>
+        <v>3437.04</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>19718.62</v>
+        <v>20052.11</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>6857.06</v>
+        <v>6926.79</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>6265.2</v>
+        <v>6309.05</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>4115.92</v>
+        <v>4049.93</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,190 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>3201.42</v>
+        <v>3185.68</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>5083-402-CM26</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>61.606.903-9</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>6783.35</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>5083-439-CM26</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>61.606.903-9</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>4886.59</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>5083-455-CM26</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>61.606.903-9</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Medyssey</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>76.485.678-3</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>6442.42</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/maule.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/maule.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maule" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Maule" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -880,7 +880,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5083-402-CM26</t>
+          <t>699866-8194-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.606.903-9</t>
+          <t>61.606.901-2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>6783.35</v>
+        <v>5854.21</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5083-439-CM26</t>
+          <t>5083-400-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>4886.59</v>
+        <v>2447.15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5083-455-CM26</t>
+          <t>5083-402-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,12 +1017,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Medyssey</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.485.678-3</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,6 +1057,189 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
+        <v>6783.35</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>4502-751-CM26</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>61.606.917-9</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>4173.3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>5083-439-CM26</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>61.606.903-9</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>4886.59</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>5083-455-CM26</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>61.606.903-9</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Medyssey</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>76.485.678-3</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
         <v>6442.42</v>
       </c>
     </row>

--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/maule.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/maule.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -615,7 +615,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>GLOBALMED SPA</t>
+          <t>GLOBALMED SpA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>GLOBALMED SPA</t>
+          <t>GLOBALMED SpA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MEDYSSEY</t>
+          <t>Medyssey</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1241,6 +1241,433 @@
       </c>
       <c r="M13" s="2" t="n">
         <v>6442.42</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>699866-8944-CM26</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>61.606.901-2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>DROGUERIA HOFMANN SAC</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>4075.56</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>4502-812-CM26</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>61.606.917-9</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>78.874.470-6</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>2365.39</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>5083-469-CM26</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>61.606.903-9</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Medyssey</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>76.485.678-3</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>18675.72</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>5083-471-CM26</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>61.606.903-9</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>4026.45</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>4502-683-CM26</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>61.606.917-9</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>TRIMED CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>11549.37</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>4817-3433-CM26</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>61.606.917-9</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>TECNIKA S A</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>2545.14</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>699866-9383-CM26</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>61.606.901-2</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>DROGUERIA HOFMANN SAC</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>4638.75</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/maule.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/maule.xlsx
@@ -928,7 +928,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1298,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1363,11 @@
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1550,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1676,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/maule.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/maule.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +810,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -945,7 +953,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5083-400-CM26</t>
+          <t>5083-402-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1000,13 +1008,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>2447.15</v>
+        <v>6783.35</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5083-402-CM26</t>
+          <t>5083-400-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1061,7 +1069,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>6783.35</v>
+        <v>2447.15</v>
       </c>
     </row>
     <row r="11">
@@ -1115,7 +1123,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1522,7 +1534,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1688,6 +1700,770 @@
       </c>
       <c r="M20" s="2" t="n">
         <v>4638.75</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>4502-896-CM26</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>61.606.917-9</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>GLOBALMED SpA</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>76.400.383-7</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>3847.58</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>4502-892-CM26</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>61.606.917-9</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>8365.74</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>4502-874-CM26</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>61.606.917-9</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>78.874.470-6</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>2898.84</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>4502-910-CM26</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>61.606.917-9</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>3910.6</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>4502-936-CM26</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>61.606.917-9</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>4488.94</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>699866-9755-CM26</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>61.606.901-2</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>DROGUERIA HOFMANN SAC</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>3903.42</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>4502-939-CM26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>61.606.917-9</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>45000.95</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>4502-938-CM26</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>61.606.917-9</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>78.874.470-6</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>4467.12</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>5083-524-CM26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>61.606.903-9</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Medyssey</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>76.485.678-3</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>6070.98</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>5083-532-CM26</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>61.606.903-9</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>GLOBALMED SpA</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>76.400.383-7</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>3223.88</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>5083-531-CM26</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>61.606.903-9</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Medyssey</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>76.485.678-3</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>18306.91</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>4502-944-CM26</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>61.606.917-9</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>78.874.470-6</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>2872.04</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/maule.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/maule.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -599,7 +599,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -888,7 +888,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>699866-8194-CM26</t>
+          <t>5083-398-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -898,12 +898,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.606.901-2</t>
+          <t>61.606.903-9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -928,32 +928,28 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>5854.21</v>
+        <v>3349.21</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5083-402-CM26</t>
+          <t>699866-8194-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -968,7 +964,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -978,12 +974,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.606.903-9</t>
+          <t>61.606.901-2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -993,22 +989,26 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>6783.35</v>
+        <v>5854.21</v>
       </c>
     </row>
     <row r="10">
@@ -1075,7 +1075,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4502-751-CM26</t>
+          <t>5083-402-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1090,22 +1090,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>61.606.903-9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1115,32 +1115,28 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>4173.3</v>
+        <v>6783.35</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5083-439-CM26</t>
+          <t>4502-751-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1155,7 +1151,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1165,12 +1161,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.606.903-9</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1180,28 +1176,32 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>4886.59</v>
+        <v>4173.3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5083-455-CM26</t>
+          <t>5083-439-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,12 +1216,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Medyssey</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.485.678-3</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1256,13 +1256,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>6442.42</v>
+        <v>4886.59</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>699866-8944-CM26</t>
+          <t>5083-455-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1272,27 +1272,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.606.901-2</t>
+          <t>61.606.903-9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1302,32 +1302,28 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>Medyssey</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.485.678-3</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>4075.56</v>
+        <v>6442.42</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4502-812-CM26</t>
+          <t>699866-8944-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1342,22 +1338,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>61.606.901-2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1367,12 +1363,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1386,13 +1382,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2365.39</v>
+        <v>4075.56</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5083-469-CM26</t>
+          <t>4502-812-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1407,7 +1403,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1417,12 +1413,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.606.903-9</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1432,28 +1428,32 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Medyssey</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.485.678-3</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>78.874.470-6</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>18675.72</v>
+        <v>2365.39</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5083-471-CM26</t>
+          <t>5083-469-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1493,12 +1493,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>Medyssey</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.485.678-3</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1508,13 +1508,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>4026.45</v>
+        <v>18675.72</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4502-683-CM26</t>
+          <t>5083-471-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1539,12 +1539,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>61.606.903-9</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1554,26 +1554,22 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>11549.37</v>
+        <v>4026.45</v>
       </c>
     </row>
     <row r="19">
@@ -1640,7 +1636,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>699866-9383-CM26</t>
+          <t>4502-683-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1655,7 +1651,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1665,12 +1661,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.606.901-2</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1680,12 +1676,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>76.556.146-9</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1699,13 +1695,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>4638.75</v>
+        <v>11549.37</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4502-896-CM26</t>
+          <t>699866-9383-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1715,27 +1711,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>oct-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>61.606.901-2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1745,28 +1741,32 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>GLOBALMED SpA</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.400.383-7</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>3847.58</v>
+        <v>4638.75</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4502-892-CM26</t>
+          <t>4502-896-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1806,32 +1806,28 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>GLOBALMED SpA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.400.383-7</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>8365.74</v>
+        <v>3847.58</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>4502-874-CM26</t>
+          <t>4502-892-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1871,12 +1867,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1890,13 +1886,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>2898.84</v>
+        <v>8365.74</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>4502-910-CM26</t>
+          <t>4502-874-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1911,7 +1907,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1936,12 +1932,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>78.874.470-6</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1955,13 +1951,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>3910.6</v>
+        <v>2898.84</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>4502-936-CM26</t>
+          <t>4502-910-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1976,7 +1972,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2020,13 +2016,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>4488.94</v>
+        <v>3910.6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>699866-9755-CM26</t>
+          <t>4502-936-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2046,17 +2042,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.606.901-2</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2066,12 +2062,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2085,13 +2081,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>3903.42</v>
+        <v>4488.94</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>4502-939-CM26</t>
+          <t>699866-9755-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2106,22 +2102,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>61.606.901-2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2131,12 +2127,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2150,13 +2146,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>45000.95</v>
+        <v>3903.42</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4502-938-CM26</t>
+          <t>4502-939-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2196,12 +2192,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2215,13 +2211,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>4467.12</v>
+        <v>45000.95</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5083-524-CM26</t>
+          <t>4502-938-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2236,7 +2232,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2246,12 +2242,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.606.903-9</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2261,28 +2257,32 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Medyssey</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.485.678-3</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+          <t>78.874.470-6</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>6070.98</v>
+        <v>4467.12</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5083-532-CM26</t>
+          <t>5083-524-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2322,12 +2322,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>GLOBALMED SpA</t>
+          <t>Medyssey</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.400.383-7</t>
+          <t>76.485.678-3</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2337,13 +2337,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>3223.88</v>
+        <v>6070.98</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5083-531-CM26</t>
+          <t>5083-532-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2383,12 +2383,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Medyssey</t>
+          <t>GLOBALMED SpA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.485.678-3</t>
+          <t>76.400.383-7</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2398,71 +2398,132 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>18306.91</v>
+        <v>3223.88</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>5083-531-CM26</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>61.606.903-9</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Medyssey</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>76.485.678-3</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>18306.91</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>4502-944-CM26</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2239-15-LR25</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
         <is>
           <t>oct-2026</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>61.606.917-9</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
         <is>
           <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="n">
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="n">
         <v>2872.04</v>
       </c>
     </row>
